--- a/Excel/Subscriptions.xlsx
+++ b/Excel/Subscriptions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75A0801B-6924-45F5-BA0E-1726BE7F4F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{75A0801B-6924-45F5-BA0E-1726BE7F4F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2EE427D-6967-48BB-82B5-3B9F94C4338F}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="1596" windowWidth="16332" windowHeight="11364" xr2:uid="{79EDE1C0-7DAB-43DF-B08E-F91666E8FE13}"/>
+    <workbookView xWindow="6144" yWindow="864" windowWidth="16332" windowHeight="11364" xr2:uid="{79EDE1C0-7DAB-43DF-B08E-F91666E8FE13}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>BBL</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>Perplexity</t>
+  </si>
+  <si>
+    <t>TRUE INTERNET</t>
+  </si>
+  <si>
+    <t>Balance</t>
   </si>
 </sst>
 </file>
@@ -97,10 +103,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,10 +442,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE55C817-E84B-4FF3-8ED2-7F8FBAA1F029}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" style="3" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -457,8 +468,11 @@
       <c r="F1" t="s">
         <v>6</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -473,6 +487,26 @@
       </c>
       <c r="F2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>9113</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46106</v>
+      </c>
+      <c r="E3">
+        <v>512.74</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="3">
+        <v>47908</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Subscriptions.xlsx
+++ b/Excel/Subscriptions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{75A0801B-6924-45F5-BA0E-1726BE7F4F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2EE427D-6967-48BB-82B5-3B9F94C4338F}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{75A0801B-6924-45F5-BA0E-1726BE7F4F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D87E7805-2269-4A88-8349-4FAD9DD77F91}"/>
   <bookViews>
-    <workbookView xWindow="6144" yWindow="864" windowWidth="16332" windowHeight="11364" xr2:uid="{79EDE1C0-7DAB-43DF-B08E-F91666E8FE13}"/>
+    <workbookView xWindow="4980" yWindow="1092" windowWidth="17304" windowHeight="11364" xr2:uid="{79EDE1C0-7DAB-43DF-B08E-F91666E8FE13}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
   <si>
     <t>BBL</t>
   </si>
@@ -66,6 +66,15 @@
   </si>
   <si>
     <t>Balance</t>
+  </si>
+  <si>
+    <t>APPLE.COM BILL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>GOOGLE ONE</t>
   </si>
 </sst>
 </file>
@@ -123,6 +132,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -442,10 +455,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE55C817-E84B-4FF3-8ED2-7F8FBAA1F029}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -477,16 +490,19 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>3118</v>
+        <v>9113</v>
       </c>
       <c r="C2" s="1">
-        <v>46105</v>
-      </c>
-      <c r="D2" s="2">
-        <v>20</v>
+        <v>46082</v>
+      </c>
+      <c r="E2">
+        <v>139</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="G2" s="3">
+        <v>43757</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -497,16 +513,122 @@
         <v>9113</v>
       </c>
       <c r="C3" s="1">
+        <v>46085</v>
+      </c>
+      <c r="E3">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="3">
+        <v>43722</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>3118</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46099</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4">
+        <v>95</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3">
+        <v>49335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>9113</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46100</v>
+      </c>
+      <c r="E5">
+        <v>239</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="3">
+        <v>49096</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>3118</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46105</v>
+      </c>
+      <c r="D6" s="2">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>9113</v>
+      </c>
+      <c r="C7" s="1">
         <v>46106</v>
       </c>
-      <c r="E3">
+      <c r="E7">
         <v>512.74</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F7" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G7" s="3">
         <v>47908</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>9113</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E8">
+        <v>139</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3">
+        <v>47908</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <f>SUM(E2:E8)</f>
+        <v>1159.74</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Subscriptions.xlsx
+++ b/Excel/Subscriptions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{75A0801B-6924-45F5-BA0E-1726BE7F4F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D87E7805-2269-4A88-8349-4FAD9DD77F91}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{75A0801B-6924-45F5-BA0E-1726BE7F4F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EF3E8A4-6AAF-424E-BCD5-207918235054}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="1092" windowWidth="17304" windowHeight="11364" xr2:uid="{79EDE1C0-7DAB-43DF-B08E-F91666E8FE13}"/>
+    <workbookView xWindow="0" yWindow="876" windowWidth="18036" windowHeight="11364" xr2:uid="{79EDE1C0-7DAB-43DF-B08E-F91666E8FE13}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>BBL</t>
   </si>
@@ -75,6 +75,15 @@
   </si>
   <si>
     <t>GOOGLE ONE</t>
+  </si>
+  <si>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>Google One Mountain</t>
+  </si>
+  <si>
+    <t>S&amp;P</t>
   </si>
 </sst>
 </file>
@@ -84,20 +93,39 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -112,11 +140,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,14 +492,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE55C817-E84B-4FF3-8ED2-7F8FBAA1F029}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -485,34 +522,34 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>9113</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="7">
         <v>46082</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>139</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="6">
         <v>43757</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3">
         <v>9113</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="8">
         <v>46085</v>
       </c>
       <c r="E3">
@@ -525,110 +562,163 @@
         <v>43722</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>3118</v>
-      </c>
-      <c r="C4" s="1">
-        <v>46099</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4">
-        <v>95</v>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C4" s="8">
+        <v>46093</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="3">
-        <v>49335</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
-      <c r="B5">
-        <v>9113</v>
+      <c r="B5" s="11">
+        <v>3118</v>
       </c>
       <c r="C5" s="1">
-        <v>46100</v>
-      </c>
-      <c r="E5">
-        <v>239</v>
+        <v>46099</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="11">
+        <v>95</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3">
-        <v>49096</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>49335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
       <c r="B6">
-        <v>3118</v>
-      </c>
-      <c r="C6" s="1">
-        <v>46105</v>
-      </c>
-      <c r="D6" s="2">
-        <v>20</v>
+        <v>9113</v>
+      </c>
+      <c r="C6" s="8">
+        <v>46100</v>
+      </c>
+      <c r="E6">
+        <v>239</v>
       </c>
       <c r="F6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G6" s="3">
+        <v>49096</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7">
         <v>9113</v>
       </c>
-      <c r="C7" s="1">
-        <v>46106</v>
+      <c r="C7" s="8">
+        <v>46101</v>
       </c>
       <c r="E7">
-        <v>512.74</v>
+        <v>95</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3">
-        <v>47908</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>0</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="11">
+        <v>3118</v>
+      </c>
+      <c r="C8" s="8">
+        <v>46105</v>
+      </c>
+      <c r="D8" s="2">
+        <v>20</v>
+      </c>
+      <c r="E8" s="11">
+        <v>675.19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
         <v>9113</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C9" s="8">
+        <v>46106</v>
+      </c>
+      <c r="E9">
+        <v>512.74</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3">
+        <v>47908</v>
+      </c>
+      <c r="H9" s="9">
+        <f>E2+E3+E6+E9</f>
+        <v>925.74</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="4">
+        <v>9113</v>
+      </c>
+      <c r="C10" s="5">
         <v>46111</v>
       </c>
-      <c r="E8">
+      <c r="E10" s="4">
         <v>139</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G10" s="6">
         <v>47908</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E9">
-        <f>SUM(E2:E8)</f>
-        <v>1159.74</v>
+      <c r="H10" s="12">
+        <f>E5+E8</f>
+        <v>770.19</v>
+      </c>
+      <c r="I10" s="4">
+        <v>396</v>
+      </c>
+      <c r="J10" s="4">
+        <f>H10+I10</f>
+        <v>1166.19</v>
+      </c>
+      <c r="K10" s="4">
+        <v>-5.83</v>
+      </c>
+      <c r="L10" s="10">
+        <f>J10+K10</f>
+        <v>1160.3600000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E11">
+        <f>SUM(E3:E10)</f>
+        <v>1790.93</v>
       </c>
     </row>
   </sheetData>
